--- a/database/Revised_Data_original_Joana_2025_10_03_completed_for_comparison.xlsx
+++ b/database/Revised_Data_original_Joana_2025_10_03_completed_for_comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joanarodriguesribeiro/Dropbox/MID in Papers/PHD_MID/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240D6BFD-FA4C-EE4B-AF0E-9922F18BCDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F72D5AA-2380-2346-8C38-EA0D6D85C8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="15100" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="1476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="1475">
   <si>
     <t>Article ID</t>
   </si>
@@ -5019,9 +5019,6 @@
     <t>00no, 1=yes</t>
   </si>
   <si>
-    <t>Type of study mentioned</t>
-  </si>
-  <si>
     <t>The patients will be divided into intervention group and control group, 281 patients were needed for each group and 562 patients would be needed totally to show this difference. Due to a possible loss of 14%, the final sample size was calculated to be 652 patients</t>
   </si>
   <si>
@@ -5125,9 +5122,6 @@
     <t>Based on the 6% decrease in 5-year OS rate in the OPD group compared with the LPD group, the sample size required for each group was estimated to be 86 patients to achieve a non-inferiority limit of 10% at a one-tailed significance level of 2.5% with a power of 80% and a balanced design (1:1 ratio).</t>
   </si>
   <si>
-    <t>Specification of SS Calculation Protocol</t>
-  </si>
-  <si>
     <t>The primary outcome of this study was the QoR-40 score at postoperative 24 h. We assume a difference in QoR-40 scores of 7.3 as a clinically important difference because this difference was reported as a minimum of 6.3 with a standard deviation of 10 using the QoR40 as a recovery tool in major spinal surgery [11, 12]. Therefore, a total of 30 patients per group were required to provide 80% power at a two-sided significance level of 0.05.</t>
   </si>
   <si>
@@ -5203,9 +5197,6 @@
   <si>
     <t xml:space="preserve">The sample size has been calculated taking the risk of conversion to open surgery as the main variable. Conversion rates of 20% in the L-LAR group and 5% in the Ta-TME group are estimated, and an α risk of 0.05 and 1-β of 0.9. The estimated number of cases to be included is 53 patients per group; with an estimated loss of 10%, the final number required is 116 patients.
 </t>
-  </si>
-  <si>
-    <t>comment: 1st outcome superiority, 2nd outcome = non-inferiority</t>
   </si>
   <si>
     <t>With a one-tailed significance level of 5%, a power of 80% and assuming a non-recurrence rate of 95% in the control group (TME) and a non-inferiority limit of 10% for the experimental group (TEM), 78 patients were needed in each group. With the estimation of 10% of possible losses, the total number of patients was 173. Sample size estimate has been calculated based on data similar to those calculated in the study by Garcia-Aguilar et al.15</t>
@@ -5543,16 +5534,29 @@
 185
 number of subjects required to 240.</t>
   </si>
+  <si>
+    <t>study type mentioned</t>
+  </si>
+  <si>
+    <t>Specification of SS Calculation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -5831,281 +5835,275 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6571,7 +6569,7 @@
         <v>1098</v>
       </c>
       <c r="AI1" s="57" t="s">
-        <v>1329</v>
+        <v>1473</v>
       </c>
       <c r="AJ1" s="57" t="s">
         <v>1104</v>
@@ -6610,7 +6608,7 @@
         <v>1103</v>
       </c>
       <c r="AV1" s="57" t="s">
-        <v>1363</v>
+        <v>1474</v>
       </c>
       <c r="AW1" s="57" t="s">
         <v>1327</v>
@@ -6674,8 +6672,8 @@
       <c r="AI2" s="56" t="s">
         <v>513</v>
       </c>
-      <c r="AJ2" s="85" t="s">
-        <v>1459</v>
+      <c r="AJ2" s="83" t="s">
+        <v>1456</v>
       </c>
       <c r="AL2" s="3" t="s">
         <v>513</v>
@@ -6683,14 +6681,14 @@
       <c r="AM2" s="3" t="s">
         <v>1272</v>
       </c>
-      <c r="AQ2" s="85" t="s">
-        <v>1435</v>
+      <c r="AQ2" s="83" t="s">
+        <v>1432</v>
       </c>
       <c r="AW2" s="56" t="s">
         <v>1328</v>
       </c>
-      <c r="AX2" s="85" t="s">
-        <v>1448</v>
+      <c r="AX2" s="83" t="s">
+        <v>1445</v>
       </c>
     </row>
     <row r="3" spans="1:52" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -6897,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="62" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="AI4" s="62">
         <v>1</v>
@@ -6906,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="AK4" s="61" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="AL4" s="7"/>
       <c r="AM4" s="7"/>
@@ -6935,7 +6933,7 @@
         <v>532</v>
       </c>
       <c r="AV4" s="61" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="AW4" s="61">
         <v>0</v>
@@ -7178,16 +7176,16 @@
         <v>0</v>
       </c>
       <c r="AH6" s="62" t="s">
+        <v>1332</v>
+      </c>
+      <c r="AI6" s="62">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="61">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="61" t="s">
         <v>1333</v>
-      </c>
-      <c r="AI6" s="62">
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="61">
-        <v>1</v>
-      </c>
-      <c r="AK6" s="61" t="s">
-        <v>1334</v>
       </c>
       <c r="AL6" s="7"/>
       <c r="AM6" s="7"/>
@@ -7529,7 +7527,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="62" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="AI9" s="62">
         <v>0</v>
@@ -7674,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="63" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="AI10" s="63">
         <v>0</v>
@@ -7710,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="AV10" s="64" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="AW10" s="64">
         <v>1</v>
@@ -7814,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="61" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="AI11" s="61">
         <v>1</v>
@@ -8189,7 +8187,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="62" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="AI14" s="62">
         <v>1</v>
@@ -8225,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="AV14" s="61" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="AW14" s="61">
         <v>1</v>
@@ -8453,7 +8451,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="61" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="AI16" s="61">
         <v>0</v>
@@ -8596,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="62" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="AI17" s="62">
         <v>1</v>
@@ -8630,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="AV17" s="65" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="AW17" s="65">
         <v>0</v>
@@ -9370,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="AH23" s="62" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="AI23" s="62">
         <v>0</v>
@@ -9447,7 +9445,7 @@
         <v>930</v>
       </c>
       <c r="L24" s="73" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="M24" s="9">
         <v>0</v>
@@ -9513,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="69" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="AI24" s="68">
         <v>0</v>
@@ -9662,7 +9660,7 @@
         <v>0</v>
       </c>
       <c r="AH25" s="63" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="AI25" s="63">
         <v>1</v>
@@ -9696,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="AV25" s="64" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="AW25" s="64">
         <v>0</v>
@@ -9806,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="AH26" s="61" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="AI26" s="61">
         <v>0</v>
@@ -9821,7 +9819,7 @@
         <v>1222</v>
       </c>
       <c r="AP26" s="74" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="AQ26" s="61">
         <v>2</v>
@@ -11125,7 +11123,7 @@
         <v>973</v>
       </c>
       <c r="L38" s="58" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -11182,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="AH38" s="61" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="AI38" s="61">
         <v>1</v>
@@ -11321,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="AH39" s="61" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="AI39" s="61">
         <v>0</v>
@@ -11709,7 +11707,7 @@
         <v>0</v>
       </c>
       <c r="AH42" s="61" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="AI42" s="61">
         <v>0</v>
@@ -11852,7 +11850,7 @@
         <v>0</v>
       </c>
       <c r="AH43" s="63" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="AI43" s="63">
         <v>0</v>
@@ -12093,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="AH45" s="61" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="AI45" s="61">
         <v>0</v>
@@ -12127,10 +12125,10 @@
         <v>532</v>
       </c>
       <c r="AW45" s="61" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="AX45" s="61" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="AY45" s="61" t="s">
         <v>532</v>
@@ -12381,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="AH48" s="62" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="AI48" s="62">
         <v>0</v>
@@ -12399,7 +12397,7 @@
         <v>1250</v>
       </c>
       <c r="AP48" s="59" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="AQ48" s="62">
         <v>1</v>
@@ -12417,7 +12415,7 @@
         <v>0</v>
       </c>
       <c r="AV48" s="65" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="AW48" s="65">
         <v>0</v>
@@ -12641,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="AH50" s="61" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="AI50" s="61">
         <v>1</v>
@@ -12674,16 +12672,16 @@
         <v>0</v>
       </c>
       <c r="AV50" s="61" t="s">
+        <v>1360</v>
+      </c>
+      <c r="AW50" s="61">
+        <v>1</v>
+      </c>
+      <c r="AX50" s="61">
+        <v>1</v>
+      </c>
+      <c r="AY50" s="61" t="s">
         <v>1361</v>
-      </c>
-      <c r="AW50" s="61">
-        <v>1</v>
-      </c>
-      <c r="AX50" s="61">
-        <v>1</v>
-      </c>
-      <c r="AY50" s="61" t="s">
-        <v>1362</v>
       </c>
       <c r="AZ50" s="20"/>
     </row>
@@ -12925,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="AH52" s="63" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="AI52" s="63">
         <v>1</v>
@@ -13270,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="AH56" s="65" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="AI56" s="65">
         <v>1</v>
@@ -13304,7 +13302,7 @@
         <v>0</v>
       </c>
       <c r="AV56" s="65" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="AW56" s="65">
         <v>0</v>
@@ -14360,7 +14358,7 @@
         <v>0</v>
       </c>
       <c r="AH70" s="62" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="AI70" s="62">
         <v>1</v>
@@ -15533,7 +15531,7 @@
         <v>0</v>
       </c>
       <c r="AH84" s="61" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="AI84" s="61">
         <v>0</v>
@@ -15670,7 +15668,7 @@
         <v>0</v>
       </c>
       <c r="AH85" s="61" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="AI85" s="61">
         <v>0</v>
@@ -15807,7 +15805,7 @@
         <v>0</v>
       </c>
       <c r="AH86" s="61" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="AI86" s="61">
         <v>1</v>
@@ -15816,7 +15814,7 @@
         <v>1</v>
       </c>
       <c r="AK86" s="61" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="AL86" s="3">
         <v>0</v>
@@ -16092,7 +16090,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="61" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="AI88" s="61">
         <v>0</v>
@@ -16226,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="AH89" s="61" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="AI89" s="61">
         <v>1</v>
@@ -16235,7 +16233,7 @@
         <v>1</v>
       </c>
       <c r="AK89" s="61" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="AL89" s="3">
         <v>0</v>
@@ -16265,7 +16263,7 @@
         <v>0</v>
       </c>
       <c r="AV89" s="61" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="AW89" s="61">
         <v>1</v>
@@ -16274,7 +16272,7 @@
         <v>1</v>
       </c>
       <c r="AY89" s="61" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="90" spans="1:52" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -16363,7 +16361,7 @@
         <v>0</v>
       </c>
       <c r="AH90" s="61" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="AI90" s="61">
         <v>0</v>
@@ -16725,7 +16723,7 @@
         <v>0</v>
       </c>
       <c r="AH93" s="61" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="AI93" s="61">
         <v>0</v>
@@ -16986,7 +16984,7 @@
         <v>1</v>
       </c>
       <c r="AH95" s="61" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="AI95" s="61">
         <v>1</v>
@@ -16995,7 +16993,7 @@
         <v>1</v>
       </c>
       <c r="AK95" s="61" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="AL95" s="3">
         <v>0</v>
@@ -17022,7 +17020,7 @@
         <v>1</v>
       </c>
       <c r="AV95" s="61" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="AW95" s="61">
         <v>1</v>
@@ -17031,7 +17029,7 @@
         <v>1</v>
       </c>
       <c r="AY95" s="61" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="96" spans="1:52" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -18150,7 +18148,7 @@
         <v>0</v>
       </c>
       <c r="AH105" s="61" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="AI105" s="61">
         <v>0</v>
@@ -18287,7 +18285,7 @@
         <v>0</v>
       </c>
       <c r="AH106" s="61" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="AI106" s="61">
         <v>0</v>
@@ -18308,7 +18306,7 @@
         <v>571</v>
       </c>
       <c r="AP106" s="78" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="AQ106" s="61">
         <v>1</v>
@@ -18326,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="AV106" s="61" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="AW106" s="61">
         <v>0</v>
@@ -18337,9 +18335,7 @@
       <c r="AY106" s="61" t="s">
         <v>532</v>
       </c>
-      <c r="AZ106" s="78" t="s">
-        <v>1387</v>
-      </c>
+      <c r="AZ106" s="78"/>
     </row>
     <row r="107" spans="1:52" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
@@ -18427,7 +18423,7 @@
         <v>0</v>
       </c>
       <c r="AH107" s="61" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="AI107" s="61">
         <v>1</v>
@@ -18436,7 +18432,7 @@
         <v>1</v>
       </c>
       <c r="AK107" s="61" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="AL107" s="3">
         <v>0</v>
@@ -18789,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="AH110" s="61" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="AI110" s="61">
         <v>0</v>
@@ -18828,7 +18824,7 @@
         <v>0</v>
       </c>
       <c r="AV110" s="61" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="AW110" s="61">
         <v>0</v>
@@ -19176,7 +19172,7 @@
         <v>0</v>
       </c>
       <c r="AH113" s="61" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="AI113" s="61">
         <v>0</v>
@@ -19677,7 +19673,7 @@
         <v>0</v>
       </c>
       <c r="AH117" s="61" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="AI117" s="61">
         <v>1</v>
@@ -20517,7 +20513,7 @@
         <v>0</v>
       </c>
       <c r="AH124" s="61" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="AI124" s="61">
         <v>0</v>
@@ -20654,7 +20650,7 @@
         <v>0</v>
       </c>
       <c r="AH125" s="61" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="AI125" s="61">
         <v>0</v>
@@ -21009,7 +21005,7 @@
         <v>0</v>
       </c>
       <c r="AH128" s="61" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="AI128" s="61">
         <v>1</v>
@@ -21030,7 +21026,7 @@
         <v>571</v>
       </c>
       <c r="AP128" s="3" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="AQ128" s="61">
         <v>1</v>
@@ -21048,7 +21044,7 @@
         <v>0</v>
       </c>
       <c r="AV128" s="61" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="AW128" s="61">
         <v>0</v>
@@ -21890,7 +21886,7 @@
         <v>0</v>
       </c>
       <c r="AH136" s="61" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="AI136" s="61">
         <v>0</v>
@@ -21920,7 +21916,7 @@
         <v>0</v>
       </c>
       <c r="AV136" s="61" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="AW136" s="61">
         <v>0</v>
@@ -22124,7 +22120,7 @@
         <v>0</v>
       </c>
       <c r="AH138" s="61" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="AI138" s="61">
         <v>1</v>
@@ -22154,7 +22150,7 @@
         <v>0</v>
       </c>
       <c r="AV138" s="61" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="AW138" s="61">
         <v>0</v>
@@ -22715,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="AH143" s="61" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="AI143" s="61">
         <v>1</v>
@@ -22745,7 +22741,7 @@
         <v>0</v>
       </c>
       <c r="AV143" s="61" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="AW143" s="61">
         <v>0</v>
@@ -23171,7 +23167,7 @@
         <v>0</v>
       </c>
       <c r="AH147" s="61" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="AI147" s="61">
         <v>1</v>
@@ -23308,7 +23304,7 @@
         <v>1</v>
       </c>
       <c r="AH148" s="61" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="AI148" s="61">
         <v>0</v>
@@ -23632,7 +23628,7 @@
         <v>0</v>
       </c>
       <c r="AH151" s="61" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="AI151" s="61">
         <v>0</v>
@@ -23656,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="AS151" s="61" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="AT151" s="61">
         <v>0</v>
@@ -23883,7 +23879,7 @@
         <v>0</v>
       </c>
       <c r="AV153" s="61" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="AW153" s="61">
         <v>0</v>
@@ -24062,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="AH155" s="61" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="AI155" s="61">
         <v>1</v>
@@ -24071,7 +24067,7 @@
         <v>1</v>
       </c>
       <c r="AK155" s="61" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="AL155" s="3">
         <v>0</v>
@@ -24095,7 +24091,7 @@
         <v>0</v>
       </c>
       <c r="AV155" s="61" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="AW155" s="61">
         <v>1</v>
@@ -24104,7 +24100,7 @@
         <v>1</v>
       </c>
       <c r="AY155" s="61" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="156" spans="1:51" s="2" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -24479,7 +24475,7 @@
         <v>0</v>
       </c>
       <c r="AH159" s="61" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="AI159" s="61">
         <v>0</v>
@@ -24512,7 +24508,7 @@
         <v>0</v>
       </c>
       <c r="AV159" s="61" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="AW159" s="61">
         <v>0</v>
@@ -24607,40 +24603,40 @@
         <v>0</v>
       </c>
       <c r="AH160" s="61" t="s">
+        <v>1412</v>
+      </c>
+      <c r="AI160" s="61">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="61">
+        <v>1</v>
+      </c>
+      <c r="AK160" s="61" t="s">
+        <v>1413</v>
+      </c>
+      <c r="AL160" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP160" s="78" t="s">
+        <v>1414</v>
+      </c>
+      <c r="AQ160" s="61">
+        <v>1</v>
+      </c>
+      <c r="AR160" s="61">
+        <v>1</v>
+      </c>
+      <c r="AS160" s="61">
+        <v>0</v>
+      </c>
+      <c r="AT160" s="61">
+        <v>0</v>
+      </c>
+      <c r="AU160" s="61">
+        <v>0</v>
+      </c>
+      <c r="AV160" s="61" t="s">
         <v>1415</v>
-      </c>
-      <c r="AI160" s="61">
-        <v>0</v>
-      </c>
-      <c r="AJ160" s="61">
-        <v>1</v>
-      </c>
-      <c r="AK160" s="61" t="s">
-        <v>1416</v>
-      </c>
-      <c r="AL160" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP160" s="78" t="s">
-        <v>1417</v>
-      </c>
-      <c r="AQ160" s="61">
-        <v>1</v>
-      </c>
-      <c r="AR160" s="61">
-        <v>1</v>
-      </c>
-      <c r="AS160" s="61">
-        <v>0</v>
-      </c>
-      <c r="AT160" s="61">
-        <v>0</v>
-      </c>
-      <c r="AU160" s="61">
-        <v>0</v>
-      </c>
-      <c r="AV160" s="61" t="s">
-        <v>1418</v>
       </c>
       <c r="AW160" s="61">
         <v>1</v>
@@ -24735,7 +24731,7 @@
         <v>0</v>
       </c>
       <c r="AH161" s="61" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="AI161" s="61">
         <v>0</v>
@@ -24860,7 +24856,7 @@
         <v>0</v>
       </c>
       <c r="AH162" s="61" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="AI162" s="61">
         <v>0</v>
@@ -24890,7 +24886,7 @@
         <v>0</v>
       </c>
       <c r="AV162" s="61" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="AW162" s="61">
         <v>0</v>
@@ -25075,7 +25071,7 @@
         <v>0</v>
       </c>
       <c r="AH164" s="61" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="AI164" s="61">
         <v>0</v>
@@ -25638,7 +25634,7 @@
         <v>0</v>
       </c>
       <c r="AH169" s="61" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="AI169" s="61">
         <v>1</v>
@@ -25668,7 +25664,7 @@
         <v>0</v>
       </c>
       <c r="AV169" s="61" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="AW169" s="61">
         <v>1</v>
@@ -25763,7 +25759,7 @@
         <v>0</v>
       </c>
       <c r="AH170" s="61" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="AI170" s="61">
         <v>1</v>
@@ -25891,7 +25887,7 @@
         <v>0</v>
       </c>
       <c r="AH171" s="61" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="AI171" s="61">
         <v>0</v>
@@ -25921,7 +25917,7 @@
         <v>0</v>
       </c>
       <c r="AV171" s="61" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="AW171" s="61">
         <v>0</v>
@@ -26016,7 +26012,7 @@
         <v>0</v>
       </c>
       <c r="AH172" s="61" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="AI172" s="61">
         <v>0</v>
@@ -26058,131 +26054,131 @@
         <v>532</v>
       </c>
     </row>
-    <row r="173" spans="1:51" s="83" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="83">
+    <row r="173" spans="1:51" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="3">
         <v>9962</v>
       </c>
-      <c r="B173" s="83" t="s">
+      <c r="B173" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C173" s="83" t="s">
+      <c r="C173" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="D173" s="83" t="s">
+      <c r="D173" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F173" s="83" t="s">
+      <c r="F173" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G173" s="83" t="s">
+      <c r="G173" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H173" s="83" t="s">
+      <c r="H173" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I173" s="83" t="s">
+      <c r="I173" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J173" s="83" t="s">
+      <c r="J173" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="K173" s="83" t="s">
+      <c r="K173" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="L173" s="83" t="s">
+      <c r="L173" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="M173" s="83">
-        <v>0</v>
-      </c>
-      <c r="N173" s="83" t="s">
-        <v>532</v>
-      </c>
-      <c r="O173" s="83" t="s">
-        <v>532</v>
-      </c>
-      <c r="P173" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q173" s="83">
-        <v>0</v>
-      </c>
-      <c r="R173" s="83">
-        <v>0</v>
-      </c>
-      <c r="S173" s="83">
-        <v>1</v>
-      </c>
-      <c r="T173" s="83">
-        <v>1</v>
-      </c>
-      <c r="U173" s="83">
+      <c r="M173" s="3">
+        <v>0</v>
+      </c>
+      <c r="N173" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="O173" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="P173" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="3">
+        <v>0</v>
+      </c>
+      <c r="R173" s="3">
+        <v>0</v>
+      </c>
+      <c r="S173" s="3">
+        <v>1</v>
+      </c>
+      <c r="T173" s="3">
+        <v>1</v>
+      </c>
+      <c r="U173" s="3">
         <v>97</v>
       </c>
-      <c r="V173" s="83">
-        <v>0</v>
-      </c>
-      <c r="W173" s="83">
-        <v>1</v>
-      </c>
-      <c r="X173" s="83">
-        <v>0</v>
-      </c>
-      <c r="Z173" s="83">
-        <v>0</v>
-      </c>
-      <c r="AA173" s="83" t="s">
+      <c r="V173" s="3">
+        <v>0</v>
+      </c>
+      <c r="W173" s="3">
+        <v>1</v>
+      </c>
+      <c r="X173" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z173" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA173" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="AB173" s="83">
-        <v>1</v>
-      </c>
-      <c r="AG173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AH173" s="84" t="s">
-        <v>1429</v>
-      </c>
-      <c r="AI173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AJ173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AK173" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AL173" s="83">
-        <v>0</v>
-      </c>
-      <c r="AN173" s="83" t="s">
+      <c r="AB173" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AH173" s="61" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AI173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AJ173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AK173" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AL173" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN173" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="AQ173" s="84">
+      <c r="AQ173" s="61">
         <v>2</v>
       </c>
-      <c r="AR173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AS173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AT173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AU173" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AV173" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AW173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AX173" s="84">
-        <v>0</v>
-      </c>
-      <c r="AY173" s="84" t="s">
+      <c r="AR173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AS173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AT173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AU173" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AV173" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AW173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AX173" s="61">
+        <v>0</v>
+      </c>
+      <c r="AY173" s="61" t="s">
         <v>532</v>
       </c>
     </row>
@@ -26217,8 +26213,8 @@
       <c r="K174" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L174" s="85" t="s">
-        <v>1431</v>
+      <c r="L174" s="83" t="s">
+        <v>1428</v>
       </c>
       <c r="M174" s="3">
         <v>0</v>
@@ -26269,7 +26265,7 @@
         <v>0</v>
       </c>
       <c r="AH174" s="61" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="AI174" s="61">
         <v>1</v>
@@ -26541,7 +26537,7 @@
         <v>0</v>
       </c>
       <c r="AH176" s="61" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="AI176" s="61">
         <v>0</v>
@@ -26870,7 +26866,7 @@
         <v>0</v>
       </c>
       <c r="AH179" s="61" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="AI179" s="61">
         <v>1</v>
@@ -26879,7 +26875,7 @@
         <v>1</v>
       </c>
       <c r="AK179" s="61" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="AL179" s="3">
         <v>0</v>
@@ -26903,7 +26899,7 @@
         <v>0</v>
       </c>
       <c r="AV179" s="61" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="AW179" s="61">
         <v>1</v>
@@ -26912,7 +26908,7 @@
         <v>1</v>
       </c>
       <c r="AY179" s="61" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="180" spans="1:51" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -26995,7 +26991,7 @@
         <v>0</v>
       </c>
       <c r="AH180" s="61" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="AI180" s="61">
         <v>0</v>
@@ -27009,7 +27005,7 @@
       <c r="AL180" s="3">
         <v>0</v>
       </c>
-      <c r="AP180" s="85"/>
+      <c r="AP180" s="83"/>
       <c r="AQ180" s="61">
         <v>1</v>
       </c>
@@ -27026,7 +27022,7 @@
         <v>0</v>
       </c>
       <c r="AV180" s="61" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="AW180" s="61">
         <v>0</v>
@@ -27118,7 +27114,7 @@
         <v>0</v>
       </c>
       <c r="AH181" s="61" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="AI181" s="61">
         <v>1</v>
@@ -27240,7 +27236,7 @@
         <v>0</v>
       </c>
       <c r="AH182" s="61" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="AI182" s="61">
         <v>1</v>
@@ -27465,7 +27461,7 @@
         <v>0</v>
       </c>
       <c r="AH184" s="61" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="AI184" s="61">
         <v>0</v>
@@ -27587,7 +27583,7 @@
         <v>0</v>
       </c>
       <c r="AH185" s="61" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="AI185" s="61">
         <v>1</v>
@@ -27617,7 +27613,7 @@
         <v>0</v>
       </c>
       <c r="AV185" s="61" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="AW185" s="61">
         <v>0</v>
@@ -27709,7 +27705,7 @@
         <v>0</v>
       </c>
       <c r="AH186" s="61" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="AI186" s="61">
         <v>0</v>
@@ -27723,8 +27719,8 @@
       <c r="AL186" s="3">
         <v>0</v>
       </c>
-      <c r="AP186" s="85" t="s">
-        <v>1446</v>
+      <c r="AP186" s="83" t="s">
+        <v>1443</v>
       </c>
       <c r="AQ186" s="61">
         <v>1</v>
@@ -27742,7 +27738,7 @@
         <v>0</v>
       </c>
       <c r="AV186" s="61" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="AW186" s="61">
         <v>1</v>
@@ -27988,7 +27984,7 @@
       <c r="AU188" s="3">
         <v>0</v>
       </c>
-      <c r="AV188" s="85" t="s">
+      <c r="AV188" s="83" t="s">
         <v>532</v>
       </c>
       <c r="AW188" s="61">
@@ -28138,7 +28134,7 @@
       <c r="AX189" s="3">
         <v>0</v>
       </c>
-      <c r="AY189" s="85" t="s">
+      <c r="AY189" s="83" t="s">
         <v>532</v>
       </c>
     </row>
@@ -28235,105 +28231,105 @@
       <c r="AX190" s="61"/>
       <c r="AY190" s="61"/>
     </row>
-    <row r="191" spans="1:51" s="86" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="86">
+    <row r="191" spans="1:51" s="84" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="84">
         <v>11587</v>
       </c>
-      <c r="B191" s="86" t="s">
+      <c r="B191" s="84" t="s">
         <v>460</v>
       </c>
-      <c r="C191" s="86" t="s">
+      <c r="C191" s="84" t="s">
         <v>461</v>
       </c>
-      <c r="D191" s="87">
+      <c r="D191" s="85">
         <v>2015</v>
       </c>
-      <c r="E191" s="86" t="s">
+      <c r="E191" s="84" t="s">
         <v>464</v>
       </c>
-      <c r="F191" s="86" t="s">
+      <c r="F191" s="84" t="s">
         <v>146</v>
       </c>
-      <c r="G191" s="86" t="s">
+      <c r="G191" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="H191" s="86" t="s">
+      <c r="H191" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="I191" s="86" t="s">
+      <c r="I191" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="J191" s="86" t="s">
+      <c r="J191" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="K191" s="86" t="s">
+      <c r="K191" s="84" t="s">
         <v>463</v>
       </c>
-      <c r="M191" s="86">
-        <v>0</v>
-      </c>
-      <c r="N191" s="86" t="s">
-        <v>532</v>
-      </c>
-      <c r="O191" s="86" t="s">
-        <v>532</v>
-      </c>
-      <c r="P191" s="86">
-        <v>0</v>
-      </c>
-      <c r="Q191" s="86">
-        <v>0</v>
-      </c>
-      <c r="R191" s="86">
-        <v>1</v>
-      </c>
-      <c r="S191" s="86">
-        <v>1</v>
-      </c>
-      <c r="T191" s="86">
-        <v>1</v>
-      </c>
-      <c r="U191" s="86">
+      <c r="M191" s="84">
+        <v>0</v>
+      </c>
+      <c r="N191" s="84" t="s">
+        <v>532</v>
+      </c>
+      <c r="O191" s="84" t="s">
+        <v>532</v>
+      </c>
+      <c r="P191" s="84">
+        <v>0</v>
+      </c>
+      <c r="Q191" s="84">
+        <v>0</v>
+      </c>
+      <c r="R191" s="84">
+        <v>1</v>
+      </c>
+      <c r="S191" s="84">
+        <v>1</v>
+      </c>
+      <c r="T191" s="84">
+        <v>1</v>
+      </c>
+      <c r="U191" s="84">
         <v>97</v>
       </c>
-      <c r="V191" s="86">
-        <v>1</v>
-      </c>
-      <c r="W191" s="86">
-        <v>0</v>
-      </c>
-      <c r="X191" s="86">
-        <v>0</v>
-      </c>
-      <c r="Z191" s="86">
-        <v>0</v>
-      </c>
-      <c r="AB191" s="86">
-        <v>0</v>
-      </c>
-      <c r="AG191" s="88"/>
-      <c r="AH191" s="88" t="s">
-        <v>532</v>
-      </c>
-      <c r="AI191" s="88"/>
-      <c r="AJ191" s="88"/>
-      <c r="AK191" s="88"/>
-      <c r="AN191" s="86" t="s">
+      <c r="V191" s="84">
+        <v>1</v>
+      </c>
+      <c r="W191" s="84">
+        <v>0</v>
+      </c>
+      <c r="X191" s="84">
+        <v>0</v>
+      </c>
+      <c r="Z191" s="84">
+        <v>0</v>
+      </c>
+      <c r="AB191" s="84">
+        <v>0</v>
+      </c>
+      <c r="AG191" s="86"/>
+      <c r="AH191" s="86" t="s">
+        <v>532</v>
+      </c>
+      <c r="AI191" s="86"/>
+      <c r="AJ191" s="86"/>
+      <c r="AK191" s="86"/>
+      <c r="AN191" s="84" t="s">
         <v>1106</v>
       </c>
-      <c r="AO191" s="89"/>
-      <c r="AP191" s="89" t="s">
+      <c r="AO191" s="87"/>
+      <c r="AP191" s="87" t="s">
         <v>1107</v>
       </c>
-      <c r="AQ191" s="90"/>
-      <c r="AR191" s="88"/>
-      <c r="AS191" s="88"/>
-      <c r="AT191" s="88"/>
-      <c r="AU191" s="88"/>
-      <c r="AV191" s="88"/>
-      <c r="AW191" s="88"/>
-      <c r="AX191" s="88"/>
-      <c r="AY191" s="88"/>
+      <c r="AQ191" s="88"/>
+      <c r="AR191" s="86"/>
+      <c r="AS191" s="86"/>
+      <c r="AT191" s="86"/>
+      <c r="AU191" s="86"/>
+      <c r="AV191" s="86"/>
+      <c r="AW191" s="86"/>
+      <c r="AX191" s="86"/>
+      <c r="AY191" s="86"/>
     </row>
     <row r="192" spans="1:51" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
@@ -28418,7 +28414,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="61" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="AI192" s="61">
         <v>0</v>
@@ -28653,143 +28649,143 @@
       <c r="AX194" s="61"/>
       <c r="AY194" s="61"/>
     </row>
-    <row r="195" spans="1:51" s="83" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="83">
+    <row r="195" spans="1:51" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="3">
         <v>11712</v>
       </c>
-      <c r="B195" s="83" t="s">
+      <c r="B195" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C195" s="83" t="s">
+      <c r="C195" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="D195" s="83" t="s">
+      <c r="D195" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E195" s="83" t="s">
+      <c r="E195" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="F195" s="83" t="s">
+      <c r="F195" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G195" s="83" t="s">
+      <c r="G195" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H195" s="83" t="s">
+      <c r="H195" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I195" s="83" t="s">
+      <c r="I195" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J195" s="83" t="s">
+      <c r="J195" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="K195" s="83" t="s">
+      <c r="K195" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="L195" s="83" t="s">
+      <c r="L195" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="M195" s="83">
-        <v>0</v>
-      </c>
-      <c r="N195" s="83" t="s">
-        <v>532</v>
-      </c>
-      <c r="O195" s="83" t="s">
-        <v>532</v>
-      </c>
-      <c r="P195" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q195" s="83">
-        <v>1</v>
-      </c>
-      <c r="R195" s="83">
-        <v>0</v>
-      </c>
-      <c r="S195" s="83">
-        <v>1</v>
-      </c>
-      <c r="T195" s="83">
-        <v>1</v>
-      </c>
-      <c r="U195" s="83">
+      <c r="M195" s="3">
+        <v>0</v>
+      </c>
+      <c r="N195" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="O195" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="P195" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="3">
+        <v>1</v>
+      </c>
+      <c r="R195" s="3">
+        <v>0</v>
+      </c>
+      <c r="S195" s="3">
+        <v>1</v>
+      </c>
+      <c r="T195" s="3">
+        <v>1</v>
+      </c>
+      <c r="U195" s="3">
         <v>130</v>
       </c>
-      <c r="V195" s="83">
-        <v>0</v>
-      </c>
-      <c r="W195" s="83">
-        <v>1</v>
-      </c>
-      <c r="X195" s="83">
-        <v>0</v>
-      </c>
-      <c r="Y195" s="83">
-        <v>1</v>
-      </c>
-      <c r="Z195" s="83">
-        <v>0</v>
-      </c>
-      <c r="AB195" s="83">
-        <v>1</v>
-      </c>
-      <c r="AC195" s="83">
-        <v>1</v>
-      </c>
-      <c r="AD195" s="83">
+      <c r="V195" s="3">
+        <v>0</v>
+      </c>
+      <c r="W195" s="3">
+        <v>1</v>
+      </c>
+      <c r="X195" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z195" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC195" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD195" s="3">
         <v>20.100000000000001</v>
       </c>
-      <c r="AE195" s="83">
-        <v>1</v>
-      </c>
-      <c r="AF195" s="83">
-        <v>1</v>
-      </c>
-      <c r="AG195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AH195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AI195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AJ195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AK195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AL195" s="83">
-        <v>0</v>
-      </c>
-      <c r="AQ195" s="84" t="s">
-        <v>1450</v>
-      </c>
-      <c r="AR195" s="84">
-        <v>0</v>
-      </c>
-      <c r="AS195" s="84">
-        <v>0</v>
-      </c>
-      <c r="AT195" s="84">
-        <v>0</v>
-      </c>
-      <c r="AU195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AV195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AW195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AX195" s="84" t="s">
-        <v>532</v>
-      </c>
-      <c r="AY195" s="84" t="s">
+      <c r="AE195" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF195" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AH195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AI195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AJ195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AK195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AL195" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ195" s="61" t="s">
+        <v>1447</v>
+      </c>
+      <c r="AR195" s="61">
+        <v>0</v>
+      </c>
+      <c r="AS195" s="61">
+        <v>0</v>
+      </c>
+      <c r="AT195" s="61">
+        <v>0</v>
+      </c>
+      <c r="AU195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AV195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AW195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AX195" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="AY195" s="61" t="s">
         <v>532</v>
       </c>
     </row>
@@ -28870,7 +28866,7 @@
         <v>0</v>
       </c>
       <c r="AH196" s="61" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="AI196" s="61">
         <v>0</v>
@@ -28992,7 +28988,7 @@
         <v>0</v>
       </c>
       <c r="AH197" s="61" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="AI197" s="61">
         <v>0</v>
@@ -29022,7 +29018,7 @@
         <v>0</v>
       </c>
       <c r="AV197" s="61" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="AW197" s="61">
         <v>0</v>
@@ -29207,7 +29203,7 @@
         <v>0</v>
       </c>
       <c r="AH199" s="61" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="AI199" s="61">
         <v>1</v>
@@ -29332,7 +29328,7 @@
         <v>0</v>
       </c>
       <c r="AH200" s="61" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="AI200" s="61">
         <v>1</v>
@@ -29341,7 +29337,7 @@
         <v>1</v>
       </c>
       <c r="AK200" s="61" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="AL200" s="3">
         <v>0</v>
@@ -29631,7 +29627,7 @@
         <v>0</v>
       </c>
       <c r="AH203" s="61" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="AI203" s="61">
         <v>1</v>
@@ -29661,7 +29657,7 @@
         <v>0</v>
       </c>
       <c r="AV203" s="61" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="AW203" s="61">
         <v>1</v>
@@ -29821,8 +29817,8 @@
       <c r="H205" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="K205" s="91" t="s">
-        <v>1460</v>
+      <c r="K205" s="89" t="s">
+        <v>1457</v>
       </c>
       <c r="L205" s="2" t="s">
         <v>545</v>
@@ -29958,7 +29954,7 @@
         <v>0</v>
       </c>
       <c r="AH206" s="61" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="AI206" s="61">
         <v>0</v>
@@ -29988,7 +29984,7 @@
         <v>0</v>
       </c>
       <c r="AV206" s="61" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="AW206" s="61">
         <v>0</v>
@@ -30159,7 +30155,7 @@
         <v>0</v>
       </c>
       <c r="AH208" s="61" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="AI208" s="61">
         <v>0</v>
@@ -30173,8 +30169,8 @@
       <c r="AL208" s="3">
         <v>0</v>
       </c>
-      <c r="AP208" s="85" t="s">
-        <v>1463</v>
+      <c r="AP208" s="83" t="s">
+        <v>1460</v>
       </c>
       <c r="AQ208" s="61">
         <v>1</v>
@@ -30192,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="AV208" s="61" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="AW208" s="61">
         <v>1</v>
@@ -30289,8 +30285,8 @@
       <c r="AG209" s="3">
         <v>1</v>
       </c>
-      <c r="AH209" s="85" t="s">
-        <v>1464</v>
+      <c r="AH209" s="83" t="s">
+        <v>1461</v>
       </c>
       <c r="AI209" s="61">
         <v>1</v>
@@ -30322,8 +30318,8 @@
       <c r="AU209" s="3">
         <v>1</v>
       </c>
-      <c r="AV209" s="85" t="s">
-        <v>1466</v>
+      <c r="AV209" s="83" t="s">
+        <v>1463</v>
       </c>
       <c r="AW209" s="61">
         <v>1</v>
@@ -30433,7 +30429,7 @@
         <v>1</v>
       </c>
       <c r="AK210" s="61" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="AL210" s="3">
         <v>0</v>
@@ -30460,7 +30456,7 @@
         <v>0</v>
       </c>
       <c r="AV210" s="61" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="AW210" s="61">
         <v>1</v>
@@ -30469,7 +30465,7 @@
         <v>1</v>
       </c>
       <c r="AY210" s="61" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="211" spans="1:51" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -30594,7 +30590,7 @@
         <v>0</v>
       </c>
       <c r="AV211" s="61" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="AW211" s="61">
         <v>0</v>
@@ -30729,7 +30725,7 @@
         <v>0</v>
       </c>
       <c r="AV212" s="61" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="AW212" s="61">
         <v>1</v>
@@ -30855,7 +30851,7 @@
         <v>0</v>
       </c>
       <c r="AV213" s="61" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="AW213" s="61">
         <v>1</v>
@@ -30953,7 +30949,7 @@
         <v>0</v>
       </c>
       <c r="AH214" s="61" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="AI214" s="61">
         <v>1</v>
@@ -30992,7 +30988,7 @@
         <v>0</v>
       </c>
       <c r="AV214" s="61" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="AW214" s="61">
         <v>0</v>
@@ -31129,7 +31125,7 @@
         <v>0</v>
       </c>
       <c r="AV215" s="61" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="AW215" s="61">
         <v>0</v>
